--- a/docs/integration-test-pack/inbound/customer360-valid.xlsx
+++ b/docs/integration-test-pack/inbound/customer360-valid.xlsx
@@ -401,530 +401,683 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>recordNo</v>
+      </c>
+      <c r="B1" t="str">
         <v>name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>vkn</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>customerType</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>email</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>phone</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>isActive</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>A001</v>
+      </c>
+      <c r="B2" t="str">
         <v>Acme Demo A.Ş.</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>1112223339</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>Kurumsal</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>info@acme.demo</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>+902121110000</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>A002</v>
+      </c>
+      <c r="B3" t="str">
         <v>Beta Demo Ltd.</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v/>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Kurumsal</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>info@beta.demo</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>+903121112222</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>A003</v>
+      </c>
+      <c r="B4" t="str">
         <v>Gama Demo Bireysel</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>7778889991</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>Bireysel</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>gama@example.demo</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>+905321113333</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Evet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>recordNo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>parentRecordNo</v>
+      </c>
+      <c r="C1" t="str">
         <v>accountKey</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>companyCode</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>externalCustomerCode</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>packageName</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>segment</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>AC001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>A001</v>
+      </c>
+      <c r="C2" t="str">
         <v>1112223339</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
         <v>COMP-UNIVERA</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>90001</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>Premium</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>Key Account</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>AC002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A002</v>
+      </c>
+      <c r="C3" t="str">
         <v>Beta Demo Ltd.</v>
       </c>
-      <c r="B3" t="str">
+      <c r="D3" t="str">
         <v/>
       </c>
-      <c r="C3" t="str">
+      <c r="E3" t="str">
         <v>90002</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
         <v>Standard</v>
       </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
         <v/>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>AC003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>A003</v>
+      </c>
+      <c r="C4" t="str">
         <v>7778889991</v>
       </c>
-      <c r="B4" t="str">
+      <c r="D4" t="str">
         <v>COMP-UNIVERA</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E4" t="str">
         <v>90003</v>
       </c>
-      <c r="D4" t="str">
+      <c r="F4" t="str">
         <v>Basic</v>
       </c>
-      <c r="E4" t="str">
+      <c r="G4" t="str">
         <v/>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>active</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>recordNo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>parentRecordNo</v>
+      </c>
+      <c r="C1" t="str">
+        <v>sourceContactId</v>
+      </c>
+      <c r="D1" t="str">
         <v>accountKey</v>
       </c>
-      <c r="B1" t="str">
+      <c r="E1" t="str">
         <v>fullName</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
         <v>title</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
         <v>email</v>
       </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
         <v>phone</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>isPrimary</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>isActive</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>C001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>A001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ERP-CN-1001</v>
+      </c>
+      <c r="D2" t="str">
         <v>1112223339</v>
       </c>
-      <c r="B2" t="str">
+      <c r="E2" t="str">
         <v>Ayşe Demo</v>
       </c>
-      <c r="C2" t="str">
+      <c r="F2" t="str">
         <v>Satın Alma Müdürü</v>
       </c>
-      <c r="D2" t="str">
+      <c r="G2" t="str">
         <v>ayse@acme.demo</v>
       </c>
-      <c r="E2" t="str">
+      <c r="H2" t="str">
         <v>+905321110001</v>
       </c>
-      <c r="F2" t="str">
-        <v>Evet</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
+        <v>Evet</v>
+      </c>
+      <c r="J2" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>C002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A001</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ERP-CN-1002</v>
+      </c>
+      <c r="D3" t="str">
         <v>1112223339</v>
       </c>
-      <c r="B3" t="str">
+      <c r="E3" t="str">
         <v>Mehmet Demo</v>
       </c>
-      <c r="C3" t="str">
+      <c r="F3" t="str">
         <v>Operasyon Şefi</v>
       </c>
-      <c r="D3" t="str">
+      <c r="G3" t="str">
         <v>mehmet@acme.demo</v>
       </c>
-      <c r="E3" t="str">
+      <c r="H3" t="str">
         <v>+905321110002</v>
       </c>
-      <c r="F3" t="str">
+      <c r="I3" t="str">
         <v>Hayır</v>
       </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>C003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>A002</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ERP-CN-2001</v>
+      </c>
+      <c r="D4" t="str">
         <v>Beta Demo Ltd.</v>
       </c>
-      <c r="B4" t="str">
+      <c r="E4" t="str">
         <v>Cem Demo</v>
       </c>
-      <c r="C4" t="str">
+      <c r="F4" t="str">
         <v>Genel Müdür</v>
       </c>
-      <c r="D4" t="str">
+      <c r="G4" t="str">
         <v>cem@beta.demo</v>
       </c>
-      <c r="E4" t="str">
+      <c r="H4" t="str">
         <v>+905321110003</v>
       </c>
-      <c r="F4" t="str">
-        <v>Evet</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
+        <v>Evet</v>
+      </c>
+      <c r="J4" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>C004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>A003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ERP-CN-3001</v>
+      </c>
+      <c r="D5" t="str">
         <v>7778889991</v>
       </c>
-      <c r="B5" t="str">
+      <c r="E5" t="str">
         <v>Selin Demo</v>
       </c>
-      <c r="C5" t="str">
+      <c r="F5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
+      <c r="G5" t="str">
         <v>selin@example.demo</v>
       </c>
-      <c r="E5" t="str">
+      <c r="H5" t="str">
         <v>+905321110004</v>
       </c>
-      <c r="F5" t="str">
-        <v>Evet</v>
-      </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
+        <v>Evet</v>
+      </c>
+      <c r="J5" t="str">
         <v>Evet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>recordNo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>parentRecordNo</v>
+      </c>
+      <c r="C1" t="str">
+        <v>sourceAddressId</v>
+      </c>
+      <c r="D1" t="str">
         <v>accountKey</v>
       </c>
-      <c r="B1" t="str">
+      <c r="E1" t="str">
         <v>type</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
         <v>label</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
         <v>line1</v>
       </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
         <v>district</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>city</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>postalCode</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>country</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>isDefault</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>isActive</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>D001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>A001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ERP-ADR-1001</v>
+      </c>
+      <c r="D2" t="str">
         <v>1112223339</v>
       </c>
-      <c r="B2" t="str">
+      <c r="E2" t="str">
         <v>Billing</v>
       </c>
-      <c r="C2" t="str">
+      <c r="F2" t="str">
         <v>Merkez Ofis</v>
       </c>
-      <c r="D2" t="str">
+      <c r="G2" t="str">
         <v>Atatürk Bulvarı No:5</v>
       </c>
-      <c r="E2" t="str">
+      <c r="H2" t="str">
         <v>Çankaya</v>
       </c>
-      <c r="F2" t="str">
+      <c r="I2" t="str">
         <v>Ankara</v>
       </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
         <v>06420</v>
       </c>
-      <c r="H2" t="str">
+      <c r="K2" t="str">
         <v>TR</v>
       </c>
-      <c r="I2" t="str">
-        <v>Evet</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
+        <v>Evet</v>
+      </c>
+      <c r="M2" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>D002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A002</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ERP-ADR-2001</v>
+      </c>
+      <c r="D3" t="str">
         <v>Beta Demo Ltd.</v>
       </c>
-      <c r="B3" t="str">
+      <c r="E3" t="str">
         <v>Headquarters</v>
       </c>
-      <c r="C3" t="str">
+      <c r="F3" t="str">
         <v>Berlin HQ</v>
       </c>
-      <c r="D3" t="str">
+      <c r="G3" t="str">
         <v>Friedrichstrasse 100</v>
       </c>
-      <c r="F3" t="str">
+      <c r="I3" t="str">
         <v>Berlin</v>
       </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
         <v>10117</v>
       </c>
-      <c r="H3" t="str">
+      <c r="K3" t="str">
         <v>DE</v>
       </c>
-      <c r="I3" t="str">
-        <v>Evet</v>
-      </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
+        <v>Evet</v>
+      </c>
+      <c r="M3" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>D003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>A003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ERP-ADR-3001</v>
+      </c>
+      <c r="D4" t="str">
         <v>7778889991</v>
       </c>
-      <c r="B4" t="str">
+      <c r="E4" t="str">
         <v>Shipping</v>
       </c>
-      <c r="C4" t="str">
+      <c r="F4" t="str">
         <v>Amsterdam Warehouse</v>
       </c>
-      <c r="D4" t="str">
+      <c r="G4" t="str">
         <v>Damrak 45</v>
       </c>
-      <c r="F4" t="str">
+      <c r="I4" t="str">
         <v>Amsterdam</v>
       </c>
-      <c r="G4" t="str">
+      <c r="J4" t="str">
         <v>1012LL</v>
       </c>
-      <c r="H4" t="str">
+      <c r="K4" t="str">
         <v>NL</v>
       </c>
-      <c r="I4" t="str">
-        <v>Evet</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
+        <v>Evet</v>
+      </c>
+      <c r="M4" t="str">
         <v>Evet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>recordNo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>parentRecordNo</v>
+      </c>
+      <c r="C1" t="str">
+        <v>parentCompanyRecordNo</v>
+      </c>
+      <c r="D1" t="str">
+        <v>sourceProjectId</v>
+      </c>
+      <c r="E1" t="str">
         <v>accountKey</v>
       </c>
-      <c r="B1" t="str">
+      <c r="F1" t="str">
         <v>accountCompanyKey</v>
       </c>
-      <c r="C1" t="str">
+      <c r="G1" t="str">
         <v>projectCode</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
         <v>projectName</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>status</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>startDate</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>endDate</v>
       </c>
-      <c r="H1" t="str">
+      <c r="L1" t="str">
         <v>isActive</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>P001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>A001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>AC001</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ERP-PRJ-1001</v>
+      </c>
+      <c r="E2" t="str">
         <v>1112223339</v>
       </c>
-      <c r="B2" t="str">
+      <c r="F2" t="str">
         <v>COMP-UNIVERA</v>
       </c>
-      <c r="C2" t="str">
+      <c r="G2" t="str">
         <v>RT-001</v>
       </c>
-      <c r="D2" t="str">
+      <c r="H2" t="str">
         <v>Rota Optimizasyon</v>
       </c>
-      <c r="E2" t="str">
+      <c r="I2" t="str">
         <v>Active</v>
       </c>
-      <c r="F2" t="str">
+      <c r="J2" t="str">
         <v>2025-03-01</v>
       </c>
-      <c r="G2" t="str">
+      <c r="K2" t="str">
         <v>2026-12-31</v>
       </c>
-      <c r="H2" t="str">
+      <c r="L2" t="str">
         <v>Evet</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>P002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A003</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>ERP-PRJ-3001</v>
+      </c>
+      <c r="E3" t="str">
         <v>7778889991</v>
       </c>
-      <c r="B3" t="str">
+      <c r="F3" t="str">
         <v/>
       </c>
-      <c r="C3" t="str">
+      <c r="G3" t="str">
         <v>BR-002</v>
       </c>
-      <c r="D3" t="str">
+      <c r="H3" t="str">
         <v>Bireysel Saha</v>
       </c>
-      <c r="E3" t="str">
+      <c r="I3" t="str">
         <v>Active</v>
       </c>
-      <c r="F3" t="str">
+      <c r="J3" t="str">
         <v>2025-06-01</v>
       </c>
-      <c r="G3" t="str">
+      <c r="K3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
+      <c r="L3" t="str">
         <v>Evet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/integration-test-pack/inbound/customer360-valid.xlsx
+++ b/docs/integration-test-pack/inbound/customer360-valid.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:N4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,6 +423,27 @@
         <v>phone</v>
       </c>
       <c r="G1" t="str">
+        <v>phoneType</v>
+      </c>
+      <c r="H1" t="str">
+        <v>phoneExtension</v>
+      </c>
+      <c r="I1" t="str">
+        <v>phone2</v>
+      </c>
+      <c r="J1" t="str">
+        <v>phone2Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>phone3</v>
+      </c>
+      <c r="L1" t="str">
+        <v>phone3Type</v>
+      </c>
+      <c r="M1" t="str">
+        <v>primaryPhoneSlot</v>
+      </c>
+      <c r="N1" t="str">
         <v>isActive</v>
       </c>
     </row>
@@ -446,6 +467,27 @@
         <v>+902121110000</v>
       </c>
       <c r="G2" t="str">
+        <v>switchboard</v>
+      </c>
+      <c r="H2" t="str">
+        <v>101</v>
+      </c>
+      <c r="I2" t="str">
+        <v>+905321119000</v>
+      </c>
+      <c r="J2" t="str">
+        <v>mobile</v>
+      </c>
+      <c r="K2" t="str">
+        <v>+905321119001</v>
+      </c>
+      <c r="L2" t="str">
+        <v>whatsapp</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2" t="str">
         <v>Evet</v>
       </c>
     </row>
@@ -469,6 +511,12 @@
         <v>+903121112222</v>
       </c>
       <c r="G3" t="str">
+        <v>work</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="str">
         <v>Evet</v>
       </c>
     </row>
@@ -492,12 +540,18 @@
         <v>+905321113333</v>
       </c>
       <c r="G4" t="str">
+        <v>mobile</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" t="str">
         <v>Evet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/integration-test-pack/inbound/customer360-valid.xlsx
+++ b/docs/integration-test-pack/inbound/customer360-valid.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,36 +414,39 @@
         <v>vkn</v>
       </c>
       <c r="D1" t="str">
+        <v>taxOffice</v>
+      </c>
+      <c r="E1" t="str">
         <v>customerType</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>email</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>phone</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>phoneType</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>phoneExtension</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>phone2</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>phone2Type</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>phone3</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>phone3Type</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>primaryPhoneSlot</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>isActive</v>
       </c>
     </row>
@@ -458,36 +461,39 @@
         <v>1112223339</v>
       </c>
       <c r="D2" t="str">
+        <v>Kadıköy Vergi Dairesi</v>
+      </c>
+      <c r="E2" t="str">
         <v>Kurumsal</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>info@acme.demo</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>+902121110000</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>switchboard</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>101</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>+905321119000</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>mobile</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>+905321119001</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>whatsapp</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>2</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>Evet</v>
       </c>
     </row>
@@ -501,22 +507,22 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Kurumsal</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>info@beta.demo</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>+903121112222</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>work</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>Evet</v>
       </c>
     </row>
@@ -530,28 +536,28 @@
       <c r="C4" t="str">
         <v>7778889991</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>Bireysel</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>gama@example.demo</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>+905321113333</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>mobile</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>Evet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>
